--- a/RAMON FRANCO/Agosto/PRORRATEO-RAMON-FRANCO-Agosto.xlsx
+++ b/RAMON FRANCO/Agosto/PRORRATEO-RAMON-FRANCO-Agosto.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Julio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\OneDrive\Desktop\RC CONSORCIO 2025\RAMON FRANCO\Agosto\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1331ED7-09F1-4CDC-8341-129737E619CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1FE9381-EED2-41AC-9DED-2A0EA5F193E5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -26,7 +26,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="115" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="83">
   <si>
     <t>Domicilio:</t>
   </si>
@@ -262,12 +262,6 @@
     <t>VALENTINA SOL, DIRESE</t>
   </si>
   <si>
-    <t>FRANCO</t>
-  </si>
-  <si>
-    <t>MARIA LAURA</t>
-  </si>
-  <si>
     <t>MICAELA</t>
   </si>
   <si>
@@ -277,7 +271,10 @@
     <t>GISELA</t>
   </si>
   <si>
-    <t>EXPENSAS - VENCIMIENTO 14/08 LIQUIDACION: JULIO</t>
+    <t>EXPENSAS - VENCIMIENTO 15/09 LIQUIDACION: AGOSTO</t>
+  </si>
+  <si>
+    <t>SERGIO</t>
   </si>
 </sst>
 </file>
@@ -421,7 +418,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="6">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -446,6 +443,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="19">
     <border>
@@ -673,7 +676,7 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="88">
+  <cellXfs count="94">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -850,6 +853,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="10" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="12" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="166" fontId="10" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="Hipervínculo" xfId="3" builtinId="8"/>
@@ -1201,7 +1212,7 @@
     <col min="4" max="4" width="10.5703125" customWidth="1"/>
     <col min="5" max="5" width="6.42578125" style="37" customWidth="1"/>
     <col min="6" max="6" width="12" style="3" customWidth="1"/>
-    <col min="7" max="7" width="7.5703125" style="3" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="3" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="9.85546875" style="3" customWidth="1"/>
     <col min="9" max="9" width="0.140625" style="3" customWidth="1"/>
     <col min="10" max="10" width="11.42578125" style="3" customWidth="1"/>
@@ -1215,7 +1226,7 @@
   <sheetData>
     <row r="1" spans="1:16" ht="26.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="74" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="B1" s="75"/>
       <c r="C1" s="75"/>
@@ -1309,7 +1320,7 @@
       <c r="A7" s="10"/>
       <c r="B7" s="25"/>
       <c r="C7" s="26">
-        <v>1251619.77</v>
+        <v>958293.75</v>
       </c>
       <c r="D7" s="26"/>
       <c r="F7" s="4"/>
@@ -1355,7 +1366,9 @@
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" s="15"/>
       <c r="B10" s="16"/>
-      <c r="C10" s="51"/>
+      <c r="C10" s="51">
+        <v>700000</v>
+      </c>
       <c r="D10" s="51"/>
       <c r="E10" s="38"/>
       <c r="F10" s="18"/>
@@ -1424,51 +1437,51 @@
       <c r="A12" s="7">
         <v>1</v>
       </c>
-      <c r="B12" s="52" t="s">
+      <c r="B12" s="88" t="s">
         <v>5</v>
       </c>
-      <c r="C12" s="64" t="s">
+      <c r="C12" s="89" t="s">
         <v>28</v>
       </c>
-      <c r="D12" s="64"/>
-      <c r="E12" s="43">
+      <c r="D12" s="89"/>
+      <c r="E12" s="90">
         <v>7.99</v>
       </c>
-      <c r="F12" s="58">
-        <v>112983.839842</v>
-      </c>
-      <c r="G12" s="44">
-        <v>0</v>
-      </c>
-      <c r="H12" s="69"/>
-      <c r="I12" s="44" t="e">
+      <c r="F12" s="91">
+        <v>222026.96665235999</v>
+      </c>
+      <c r="G12" s="92">
+        <v>0</v>
+      </c>
+      <c r="H12" s="91"/>
+      <c r="I12" s="92" t="e">
         <f>C9*E12/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J12" s="44">
-        <f t="shared" ref="J12:J19" si="0">F12-G12-H12</f>
-        <v>112983.839842</v>
-      </c>
-      <c r="K12" s="44"/>
-      <c r="L12" s="45">
-        <f>(J12+K12)*8%</f>
-        <v>9038.7071873599998</v>
-      </c>
-      <c r="M12" s="45">
+      <c r="J12" s="92">
+        <f>F12-G12-H12</f>
+        <v>222026.96665235999</v>
+      </c>
+      <c r="K12" s="92"/>
+      <c r="L12" s="93">
+        <f>IF(J11&gt;0,(J12+K12)*8%,0)</f>
+        <v>17762.157332188799</v>
+      </c>
+      <c r="M12" s="93">
         <f>J12+L12+K12</f>
-        <v>122022.54702935999</v>
-      </c>
-      <c r="N12" s="44">
+        <v>239789.12398454879</v>
+      </c>
+      <c r="N12" s="92">
         <f>C7*E12/100</f>
-        <v>100004.41962300001</v>
-      </c>
-      <c r="O12" s="44">
-        <f t="shared" ref="O12:O29" si="1">C$10*E12/100</f>
-        <v>0</v>
-      </c>
-      <c r="P12" s="45">
+        <v>76567.670624999999</v>
+      </c>
+      <c r="O12" s="92">
+        <f>C$10*E12/100</f>
+        <v>55930</v>
+      </c>
+      <c r="P12" s="93">
         <f>N12+M12+O12</f>
-        <v>222026.96665235999</v>
+        <v>372286.79460954876</v>
       </c>
     </row>
     <row r="13" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1488,14 +1501,14 @@
         <v>6.05</v>
       </c>
       <c r="F13" s="58">
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="G13" s="44">
         <v>0</v>
       </c>
       <c r="H13" s="69">
         <f>F13</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="I13" s="44" t="e">
         <f>C9*E13/100</f>
@@ -1507,24 +1520,24 @@
       </c>
       <c r="K13" s="44"/>
       <c r="L13" s="45">
-        <f t="shared" ref="L13:L29" si="2">(J13+K13)*8%</f>
+        <f>IF(J12&gt;0,(J13+K13)*8%,0)</f>
         <v>0</v>
       </c>
       <c r="M13" s="45">
-        <f t="shared" ref="M13:M15" si="3">J13+L13+K13</f>
+        <f t="shared" ref="M13:M15" si="0">J13+L13+K13</f>
         <v>0</v>
       </c>
       <c r="N13" s="44">
         <f>C7*E13/100</f>
-        <v>75722.996085000006</v>
+        <v>57976.771874999999</v>
       </c>
       <c r="O13" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C$10*E13/100</f>
+        <v>42350</v>
       </c>
       <c r="P13" s="45">
-        <f t="shared" ref="P13:P29" si="4">N13+M13+O13</f>
-        <v>75722.996085000006</v>
+        <f t="shared" ref="P13:P29" si="1">N13+M13+O13</f>
+        <v>100326.77187500001</v>
       </c>
     </row>
     <row r="14" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1538,20 +1551,20 @@
         <v>29</v>
       </c>
       <c r="D14" s="64" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="E14" s="43">
         <v>6.02</v>
       </c>
       <c r="F14" s="58">
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="G14" s="44">
         <v>0</v>
       </c>
       <c r="H14" s="69">
-        <f t="shared" ref="H14:H29" si="5">F14</f>
-        <v>85126.747916000008</v>
+        <f>F14</f>
+        <v>75347.510154000003</v>
       </c>
       <c r="I14" s="44" t="e">
         <f>C9*E14/100</f>
@@ -1563,24 +1576,24 @@
       </c>
       <c r="K14" s="44"/>
       <c r="L14" s="45">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="L14:L29" si="2">(J14+K14)*8%</f>
         <v>0</v>
       </c>
       <c r="M14" s="45">
-        <f t="shared" si="3"/>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
       <c r="N14" s="44">
         <f>C7*E14/100</f>
-        <v>75347.510154000003</v>
+        <v>57689.283750000002</v>
       </c>
       <c r="O14" s="44">
+        <f>C$10*E14/100</f>
+        <v>42140</v>
+      </c>
+      <c r="P14" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P14" s="45">
-        <f t="shared" si="4"/>
-        <v>75347.510154000003</v>
+        <v>99829.283750000002</v>
       </c>
     </row>
     <row r="15" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1598,38 +1611,41 @@
         <v>7.63</v>
       </c>
       <c r="F15" s="60">
-        <v>107893.20375400002</v>
+        <v>212023.24850532002</v>
       </c>
       <c r="G15" s="46"/>
-      <c r="H15" s="69"/>
+      <c r="H15" s="69">
+        <f>F15</f>
+        <v>212023.24850532002</v>
+      </c>
       <c r="I15" s="44" t="e">
         <f>C9*E15/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J15" s="44">
-        <f t="shared" si="0"/>
-        <v>107893.20375400002</v>
+        <f>F15-G15-H15</f>
+        <v>0</v>
       </c>
       <c r="K15" s="48"/>
       <c r="L15" s="45">
         <f t="shared" si="2"/>
-        <v>8631.4563003200019</v>
+        <v>0</v>
       </c>
       <c r="M15" s="45">
-        <f t="shared" si="3"/>
-        <v>116524.66005432002</v>
+        <f t="shared" si="0"/>
+        <v>0</v>
       </c>
       <c r="N15" s="50">
         <f>C7*E15/100</f>
-        <v>95498.588451000003</v>
+        <v>73117.813125000001</v>
       </c>
       <c r="O15" s="44">
+        <f>C$10*E15/100</f>
+        <v>53410</v>
+      </c>
+      <c r="P15" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P15" s="45">
-        <f t="shared" si="4"/>
-        <v>212023.24850532002</v>
+        <v>126527.813125</v>
       </c>
     </row>
     <row r="16" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1643,27 +1659,27 @@
         <v>33</v>
       </c>
       <c r="D16" s="64" t="s">
-        <v>79</v>
+        <v>82</v>
       </c>
       <c r="E16" s="43">
         <v>6.05</v>
       </c>
       <c r="F16" s="58">
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="G16" s="46">
         <v>0</v>
       </c>
       <c r="H16" s="69">
         <f>F16</f>
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="I16" s="44" t="e">
         <f>C9*E16/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J16" s="44">
-        <f t="shared" si="0"/>
+        <f>F16-G16-H16</f>
         <v>0</v>
       </c>
       <c r="K16" s="44"/>
@@ -1677,15 +1693,15 @@
       </c>
       <c r="N16" s="44">
         <f>C7*E16/100</f>
-        <v>75722.996085000006</v>
+        <v>57976.771874999999</v>
       </c>
       <c r="O16" s="44">
+        <f>C$10*E16/100</f>
+        <v>42350</v>
+      </c>
+      <c r="P16" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P16" s="45">
-        <f t="shared" si="4"/>
-        <v>75722.996085000006</v>
+        <v>100326.77187500001</v>
       </c>
     </row>
     <row r="17" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1699,27 +1715,27 @@
         <v>33</v>
       </c>
       <c r="D17" s="64" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E17" s="43">
         <v>6.02</v>
       </c>
       <c r="F17" s="58">
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="G17" s="44">
         <v>0</v>
       </c>
       <c r="H17" s="69">
         <f>F17</f>
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="I17" s="44" t="e">
         <f>C9*E17/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J17" s="44">
-        <f t="shared" si="0"/>
+        <f>F17-G17-H17</f>
         <v>0</v>
       </c>
       <c r="K17" s="44"/>
@@ -1728,20 +1744,20 @@
         <v>0</v>
       </c>
       <c r="M17" s="45">
-        <f t="shared" ref="M17:M29" si="6">J17+L17+K17</f>
+        <f t="shared" ref="M17:M29" si="3">J17+L17+K17</f>
         <v>0</v>
       </c>
       <c r="N17" s="44">
         <f>C7*E17/100</f>
-        <v>75347.510154000003</v>
+        <v>57689.283750000002</v>
       </c>
       <c r="O17" s="44">
+        <f>C$10*E17/100</f>
+        <v>42140</v>
+      </c>
+      <c r="P17" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P17" s="45">
-        <f t="shared" si="4"/>
-        <v>75347.510154000003</v>
+        <v>99829.283750000002</v>
       </c>
     </row>
     <row r="18" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1759,21 +1775,21 @@
         <v>7.63</v>
       </c>
       <c r="F18" s="58">
-        <v>107893.20375400002</v>
+        <v>95498.588451000003</v>
       </c>
       <c r="G18" s="44">
         <v>0</v>
       </c>
       <c r="H18" s="69">
         <f>F18</f>
-        <v>107893.20375400002</v>
+        <v>95498.588451000003</v>
       </c>
       <c r="I18" s="44" t="e">
         <f>C9*E18/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J18" s="44">
-        <f t="shared" si="0"/>
+        <f>F18-G18-H18</f>
         <v>0</v>
       </c>
       <c r="K18" s="44"/>
@@ -1782,20 +1798,20 @@
         <v>0</v>
       </c>
       <c r="M18" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N18" s="44">
         <f>C7*E18/100</f>
-        <v>95498.588451000003</v>
+        <v>73117.813125000001</v>
       </c>
       <c r="O18" s="44">
+        <f>C$10*E18/100</f>
+        <v>53410</v>
+      </c>
+      <c r="P18" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P18" s="45">
-        <f t="shared" si="4"/>
-        <v>95498.588451000003</v>
+        <v>126527.813125</v>
       </c>
     </row>
     <row r="19" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1808,50 +1824,45 @@
       <c r="C19" s="64" t="s">
         <v>35</v>
       </c>
-      <c r="D19" s="64" t="s">
-        <v>78</v>
-      </c>
+      <c r="D19" s="64"/>
       <c r="E19" s="43">
         <v>6.05</v>
       </c>
       <c r="F19" s="58">
-        <v>85550.96759</v>
+        <v>75722.996085000006</v>
       </c>
       <c r="G19" s="44">
         <v>0</v>
       </c>
-      <c r="H19" s="69">
-        <f>F19</f>
-        <v>85550.96759</v>
-      </c>
+      <c r="H19" s="69"/>
       <c r="I19" s="44" t="e">
         <f>C9*E19/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J19" s="44">
-        <f t="shared" si="0"/>
-        <v>0</v>
+        <f>F19-G19-H19</f>
+        <v>75722.996085000006</v>
       </c>
       <c r="K19" s="44"/>
       <c r="L19" s="45">
         <f t="shared" si="2"/>
-        <v>0</v>
+        <v>6057.8396868000009</v>
       </c>
       <c r="M19" s="45">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>81780.835771800004</v>
       </c>
       <c r="N19" s="44">
         <f>C7*E19/100</f>
-        <v>75722.996085000006</v>
+        <v>57976.771874999999</v>
       </c>
       <c r="O19" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C$10*E19/100</f>
+        <v>42350</v>
       </c>
       <c r="P19" s="45">
         <f>N19+M19+O19</f>
-        <v>75722.996085000006</v>
+        <v>182107.6076468</v>
       </c>
     </row>
     <row r="20" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1869,14 +1880,14 @@
         <v>6.02</v>
       </c>
       <c r="F20" s="58">
-        <v>85126.747916000008</v>
+        <v>75347.510154000003</v>
       </c>
       <c r="G20" s="44">
         <v>0</v>
       </c>
       <c r="H20" s="69">
-        <f t="shared" si="5"/>
-        <v>85126.747916000008</v>
+        <f>F20+50000</f>
+        <v>125347.510154</v>
       </c>
       <c r="I20" s="44" t="e">
         <f>C9*E20/100</f>
@@ -1885,27 +1896,27 @@
       <c r="J20" s="44"/>
       <c r="K20" s="44">
         <f>F20-H20</f>
-        <v>0</v>
+        <v>-50000</v>
       </c>
       <c r="L20" s="45">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f>IF(J19&gt;0,(J20+K20)*8%,0)</f>
+        <v>-4000</v>
       </c>
       <c r="M20" s="45">
-        <f t="shared" si="6"/>
-        <v>0</v>
+        <f t="shared" si="3"/>
+        <v>-54000</v>
       </c>
       <c r="N20" s="44">
         <f>C7*E20/100</f>
-        <v>75347.510154000003</v>
+        <v>57689.283750000002</v>
       </c>
       <c r="O20" s="44">
-        <f t="shared" si="1"/>
-        <v>0</v>
+        <f>C$10*E20/100</f>
+        <v>42140</v>
       </c>
       <c r="P20" s="45">
-        <f t="shared" si="4"/>
-        <v>75347.510154000003</v>
+        <f>N20+M20+O20</f>
+        <v>45829.283750000002</v>
       </c>
     </row>
     <row r="21" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1923,21 +1934,21 @@
         <v>21.2</v>
       </c>
       <c r="F21" s="58">
-        <v>299781.90295999998</v>
+        <v>265343.39123999997</v>
       </c>
       <c r="G21" s="44">
         <v>0</v>
       </c>
       <c r="H21" s="69">
         <f>F21</f>
-        <v>299781.90295999998</v>
+        <v>265343.39123999997</v>
       </c>
       <c r="I21" s="44" t="e">
         <f>C9*E21/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J21" s="44">
-        <f t="shared" ref="J21:J29" si="7">F21-G21-H21</f>
+        <f>F21-G21-H21</f>
         <v>0</v>
       </c>
       <c r="K21" s="44"/>
@@ -1946,20 +1957,20 @@
         <v>0</v>
       </c>
       <c r="M21" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N21" s="44">
         <f>C7*E21/100</f>
-        <v>265343.39123999997</v>
+        <v>203158.27499999999</v>
       </c>
       <c r="O21" s="44">
+        <f>C$10*E21/100</f>
+        <v>148400</v>
+      </c>
+      <c r="P21" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P21" s="45">
-        <f t="shared" si="4"/>
-        <v>265343.39123999997</v>
+        <v>351558.27500000002</v>
       </c>
     </row>
     <row r="22" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -1979,21 +1990,21 @@
         <v>6.81</v>
       </c>
       <c r="F22" s="58">
-        <v>96297.865997999994</v>
+        <v>85235.306337000002</v>
       </c>
       <c r="G22" s="44">
         <v>0</v>
       </c>
       <c r="H22" s="69">
         <f>F22</f>
-        <v>96297.865997999994</v>
+        <v>85235.306337000002</v>
       </c>
       <c r="I22" s="44" t="e">
         <f>C9*E22/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J22" s="44">
-        <f t="shared" si="7"/>
+        <f>F22-G22-H22</f>
         <v>0</v>
       </c>
       <c r="K22" s="44"/>
@@ -2002,20 +2013,20 @@
         <v>0</v>
       </c>
       <c r="M22" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N22" s="44">
         <f>C7*E22/100</f>
-        <v>85235.306337000002</v>
+        <v>65259.804375</v>
       </c>
       <c r="O22" s="44">
+        <f>C$10*E22/100</f>
+        <v>47670</v>
+      </c>
+      <c r="P22" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P22" s="45">
-        <f t="shared" si="4"/>
-        <v>85235.306337000002</v>
+        <v>112929.80437500001</v>
       </c>
     </row>
     <row r="23" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2035,20 +2046,20 @@
         <v>6.52</v>
       </c>
       <c r="F23" s="69">
-        <v>92197.075815999997</v>
+        <v>81605.609003999998</v>
       </c>
       <c r="G23" s="44">
         <v>0</v>
       </c>
       <c r="H23" s="69">
         <f>F23</f>
-        <v>92197.075815999997</v>
+        <v>81605.609003999998</v>
       </c>
       <c r="I23" s="44">
         <v>0</v>
       </c>
       <c r="J23" s="44">
-        <f t="shared" si="7"/>
+        <f>F23-G23-H23</f>
         <v>0</v>
       </c>
       <c r="K23" s="44"/>
@@ -2062,119 +2073,119 @@
       </c>
       <c r="N23" s="44">
         <f>C7*E23/100</f>
-        <v>81605.609003999998</v>
+        <v>62480.752500000002</v>
       </c>
       <c r="O23" s="44">
+        <f>C$10*E23/100</f>
+        <v>45640</v>
+      </c>
+      <c r="P23" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P23" s="45">
-        <f t="shared" si="4"/>
-        <v>81605.609003999998</v>
+        <v>108120.7525</v>
       </c>
     </row>
     <row r="24" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A24" s="7">
         <v>14</v>
       </c>
-      <c r="B24" s="52" t="s">
+      <c r="B24" s="88" t="s">
         <v>56</v>
       </c>
-      <c r="C24" s="64" t="s">
+      <c r="C24" s="89" t="s">
         <v>44</v>
       </c>
-      <c r="D24" s="64"/>
-      <c r="E24" s="43">
+      <c r="D24" s="89"/>
+      <c r="E24" s="90">
         <v>1.18</v>
       </c>
-      <c r="F24" s="58">
-        <v>477529.55540258653</v>
-      </c>
-      <c r="G24" s="44">
-        <v>0</v>
-      </c>
-      <c r="H24" s="69"/>
-      <c r="I24" s="44" t="e">
+      <c r="F24" s="91">
+        <v>530501.03312079341</v>
+      </c>
+      <c r="G24" s="92">
+        <v>0</v>
+      </c>
+      <c r="H24" s="91"/>
+      <c r="I24" s="92" t="e">
         <f>C9*E24/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J24" s="44">
-        <f t="shared" si="7"/>
-        <v>477529.55540258653</v>
-      </c>
-      <c r="K24" s="44"/>
-      <c r="L24" s="45">
+      <c r="J24" s="92">
+        <f>F24-G24-H24</f>
+        <v>530501.03312079341</v>
+      </c>
+      <c r="K24" s="92"/>
+      <c r="L24" s="93">
         <f t="shared" si="2"/>
-        <v>38202.364432206923</v>
-      </c>
-      <c r="M24" s="45">
-        <f t="shared" si="6"/>
-        <v>515731.91983479343</v>
-      </c>
-      <c r="N24" s="44">
+        <v>42440.082649663476</v>
+      </c>
+      <c r="M24" s="93">
+        <f t="shared" si="3"/>
+        <v>572941.11577045685</v>
+      </c>
+      <c r="N24" s="92">
         <f>C7*E24/100</f>
-        <v>14769.113286</v>
-      </c>
-      <c r="O24" s="44">
+        <v>11307.866249999999</v>
+      </c>
+      <c r="O24" s="92">
+        <f>C$10*E24/100</f>
+        <v>8260</v>
+      </c>
+      <c r="P24" s="93">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P24" s="45">
-        <f t="shared" si="4"/>
-        <v>530501.03312079341</v>
+        <v>592508.98202045681</v>
       </c>
     </row>
     <row r="25" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A25" s="7">
         <v>15</v>
       </c>
-      <c r="B25" s="52" t="s">
+      <c r="B25" s="88" t="s">
         <v>57</v>
       </c>
-      <c r="C25" s="64" t="s">
+      <c r="C25" s="89" t="s">
         <v>46</v>
       </c>
-      <c r="D25" s="64"/>
-      <c r="E25" s="43">
+      <c r="D25" s="89"/>
+      <c r="E25" s="90">
         <v>1.17</v>
       </c>
-      <c r="F25" s="58">
-        <v>471325.85123972566</v>
-      </c>
-      <c r="G25" s="44">
-        <v>0</v>
-      </c>
-      <c r="H25" s="69">
-        <v>0</v>
-      </c>
-      <c r="I25" s="44" t="e">
+      <c r="F25" s="91">
+        <v>523675.87064790376</v>
+      </c>
+      <c r="G25" s="92">
+        <v>0</v>
+      </c>
+      <c r="H25" s="91">
+        <v>0</v>
+      </c>
+      <c r="I25" s="92" t="e">
         <f>C9*E25/100</f>
         <v>#VALUE!</v>
       </c>
-      <c r="J25" s="44">
-        <f t="shared" si="7"/>
-        <v>471325.85123972566</v>
-      </c>
-      <c r="K25" s="44"/>
-      <c r="L25" s="45">
+      <c r="J25" s="92">
+        <f>F25-G25-H25</f>
+        <v>523675.87064790376</v>
+      </c>
+      <c r="K25" s="92"/>
+      <c r="L25" s="93">
         <f t="shared" si="2"/>
-        <v>37706.068099178054</v>
-      </c>
-      <c r="M25" s="45">
-        <f t="shared" si="6"/>
-        <v>509031.91933890374</v>
-      </c>
-      <c r="N25" s="44">
+        <v>41894.069651832302</v>
+      </c>
+      <c r="M25" s="93">
+        <f t="shared" si="3"/>
+        <v>565569.9402997361</v>
+      </c>
+      <c r="N25" s="92">
         <f>C7*E25/100</f>
-        <v>14643.951309</v>
-      </c>
-      <c r="O25" s="44">
+        <v>11212.036875</v>
+      </c>
+      <c r="O25" s="92">
+        <f>C$10*E25/100</f>
+        <v>8190</v>
+      </c>
+      <c r="P25" s="93">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P25" s="45">
-        <f t="shared" si="4"/>
-        <v>523675.87064790376</v>
+        <v>584971.97717473609</v>
       </c>
     </row>
     <row r="26" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2192,21 +2203,21 @@
         <v>1.06</v>
       </c>
       <c r="F26" s="58">
-        <v>14989.095148000002</v>
+        <v>13267.169562000001</v>
       </c>
       <c r="G26" s="44">
         <v>0</v>
       </c>
       <c r="H26" s="69">
         <f>F26</f>
-        <v>14989.095148000002</v>
+        <v>13267.169562000001</v>
       </c>
       <c r="I26" s="44" t="e">
         <f>C9*E26/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J26" s="44">
-        <f t="shared" si="7"/>
+        <f>F26-G26-H26</f>
         <v>0</v>
       </c>
       <c r="K26" s="44"/>
@@ -2215,20 +2226,20 @@
         <v>0</v>
       </c>
       <c r="M26" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N26" s="44">
         <f>C7*E26/100</f>
-        <v>13267.169562000001</v>
+        <v>10157.91375</v>
       </c>
       <c r="O26" s="44">
+        <f>C$10*E26/100</f>
+        <v>7420</v>
+      </c>
+      <c r="P26" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P26" s="45">
-        <f t="shared" si="4"/>
-        <v>13267.169562000001</v>
+        <v>17577.91375</v>
       </c>
     </row>
     <row r="27" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2239,14 +2250,14 @@
         <v>59</v>
       </c>
       <c r="C27" s="64" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D27" s="64"/>
       <c r="E27" s="43">
         <v>0.51</v>
       </c>
       <c r="F27" s="58">
-        <v>34399.093444696315</v>
+        <v>43534.28174727202</v>
       </c>
       <c r="G27" s="44">
         <v>0</v>
@@ -2257,29 +2268,29 @@
         <v>#VALUE!</v>
       </c>
       <c r="J27" s="44">
-        <f t="shared" si="7"/>
-        <v>34399.093444696315</v>
+        <f>F27-G27-H27</f>
+        <v>43534.28174727202</v>
       </c>
       <c r="K27" s="44"/>
       <c r="L27" s="45">
         <f t="shared" si="2"/>
-        <v>2751.9274755757051</v>
+        <v>3482.7425397817615</v>
       </c>
       <c r="M27" s="45">
-        <f t="shared" si="6"/>
-        <v>37151.020920272022</v>
+        <f t="shared" si="3"/>
+        <v>47017.024287053784</v>
       </c>
       <c r="N27" s="44">
         <f>C7*E27/100</f>
-        <v>6383.2608270000001</v>
+        <v>4887.2981250000003</v>
       </c>
       <c r="O27" s="44">
+        <f>C$10*E27/100</f>
+        <v>3570</v>
+      </c>
+      <c r="P27" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P27" s="45">
-        <f t="shared" si="4"/>
-        <v>43534.28174727202</v>
+        <v>55474.322412053785</v>
       </c>
     </row>
     <row r="28" spans="1:16" ht="15" customHeight="1" x14ac:dyDescent="0.25">
@@ -2297,21 +2308,21 @@
         <v>0.27</v>
       </c>
       <c r="F28" s="58">
-        <v>3817.9770660000004</v>
+        <v>3379.3733790000006</v>
       </c>
       <c r="G28" s="44">
         <v>0</v>
       </c>
       <c r="H28" s="69">
-        <f t="shared" si="5"/>
-        <v>3817.9770660000004</v>
+        <f>F28</f>
+        <v>3379.3733790000006</v>
       </c>
       <c r="I28" s="44" t="e">
         <f>C9*E28/100</f>
         <v>#VALUE!</v>
       </c>
       <c r="J28" s="44">
-        <f t="shared" si="7"/>
+        <f>F28-G28-H28</f>
         <v>0</v>
       </c>
       <c r="K28" s="44"/>
@@ -2320,20 +2331,20 @@
         <v>0</v>
       </c>
       <c r="M28" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N28" s="44">
         <f>C7*E28/100</f>
-        <v>3379.3733790000006</v>
+        <v>2587.3931250000005</v>
       </c>
       <c r="O28" s="44">
+        <f>C$10*E28/100</f>
+        <v>1890</v>
+      </c>
+      <c r="P28" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P28" s="45">
-        <f t="shared" si="4"/>
-        <v>3379.3733790000006</v>
+        <v>4477.3931250000005</v>
       </c>
     </row>
     <row r="29" spans="1:16" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -2349,18 +2360,18 @@
         <v>1.82</v>
       </c>
       <c r="F29" s="59">
-        <v>25735.993556000005</v>
+        <v>22779.479813999998</v>
       </c>
       <c r="G29" s="44">
         <v>0</v>
       </c>
       <c r="H29" s="69">
-        <f t="shared" si="5"/>
-        <v>25735.993556000005</v>
+        <f>F29</f>
+        <v>22779.479813999998</v>
       </c>
       <c r="I29" s="48"/>
       <c r="J29" s="44">
-        <f t="shared" si="7"/>
+        <f>F29-G29-H29</f>
         <v>0</v>
       </c>
       <c r="K29" s="48"/>
@@ -2369,20 +2380,20 @@
         <v>0</v>
       </c>
       <c r="M29" s="45">
-        <f t="shared" si="6"/>
+        <f t="shared" si="3"/>
         <v>0</v>
       </c>
       <c r="N29" s="48">
         <f>C7*E29/100</f>
-        <v>22779.479813999998</v>
+        <v>17440.946250000001</v>
       </c>
       <c r="O29" s="44">
+        <f>C$10*E29/100</f>
+        <v>12740</v>
+      </c>
+      <c r="P29" s="45">
         <f t="shared" si="1"/>
-        <v>0</v>
-      </c>
-      <c r="P29" s="45">
-        <f t="shared" si="4"/>
-        <v>22779.479813999998</v>
+        <v>30180.946250000001</v>
       </c>
     </row>
     <row r="30" spans="1:16" s="2" customFormat="1" ht="21.75" thickBot="1" x14ac:dyDescent="0.4">
@@ -2395,7 +2406,7 @@
       <c r="E30" s="42"/>
       <c r="F30" s="54">
         <f>SUM(F12:F29)</f>
-        <v>2356877.8044990078</v>
+        <v>2552081.8371776491</v>
       </c>
       <c r="G30" s="54">
         <f>SUM(G12:G29)</f>
@@ -2403,30 +2414,30 @@
       </c>
       <c r="H30" s="62">
         <f>SUM(H12:H29)</f>
-        <v>1152746.2608159999</v>
+        <v>1206620.6889243203</v>
       </c>
       <c r="I30" s="54"/>
       <c r="J30" s="62">
         <f>SUM(J12:J29)</f>
-        <v>1204131.5436830085</v>
+        <v>1395461.1482533291</v>
       </c>
       <c r="K30" s="54"/>
       <c r="L30" s="68">
         <f>L12+L13+L14+L15+L16+L17+L18+L19+L20+L21+L22+L23+L24+L25+L26+L27+L28+L29</f>
-        <v>96330.523494640685</v>
+        <v>107636.89186026633</v>
       </c>
       <c r="M30" s="55"/>
       <c r="N30" s="70">
         <f>SUM(N12:N29)</f>
-        <v>1251619.77</v>
+        <v>958293.74999999965</v>
       </c>
       <c r="O30" s="56">
         <f>SUM(O12:O29)</f>
-        <v>0</v>
+        <v>700000</v>
       </c>
       <c r="P30" s="57">
         <f>SUM(P16:P29) +P15+P14+P13+P12</f>
-        <v>2552081.8371776491</v>
+        <v>3111391.7901135944</v>
       </c>
     </row>
     <row r="31" spans="1:16" ht="34.5" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
